--- a/public/data/Improv_Set_02_Tell_Me_About_Yourself.xlsx
+++ b/public/data/Improv_Set_02_Tell_Me_About_Yourself.xlsx
@@ -397,174 +397,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:R63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Set 02 • Tell Me About Yourself (Self Pitch &amp; Work Experience)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>60 progressive deduction items for self-introductions, professional skills, and interview reflexes based on Level B Day 3.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
         <v>Session</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B3" t="str">
         <v>Item</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C3" t="str">
         <v>hc-total</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D3" t="str">
         <v>hint-1</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E3" t="str">
+        <v>hint-2</v>
+      </c>
+      <c r="F3" t="str">
+        <v>hint-3</v>
+      </c>
+      <c r="G3" t="str">
+        <v>hint-4</v>
+      </c>
+      <c r="H3" t="str">
+        <v>hint-5</v>
+      </c>
+      <c r="I3" t="str">
         <v>hint-1-translation</v>
       </c>
-      <c r="F1" t="str">
+      <c r="J3" t="str">
+        <v>hint-2-translation</v>
+      </c>
+      <c r="K3" t="str">
+        <v>hint-3-translation</v>
+      </c>
+      <c r="L3" t="str">
+        <v>hint-4-translation</v>
+      </c>
+      <c r="M3" t="str">
+        <v>hint-5-translation</v>
+      </c>
+      <c r="N3" t="str">
         <v>hint-1-type / function</v>
       </c>
-      <c r="G1" t="str">
-        <v>hint-2</v>
-      </c>
-      <c r="H1" t="str">
-        <v>hint-2-translation</v>
-      </c>
-      <c r="I1" t="str">
+      <c r="O3" t="str">
         <v>hint-2-type / function</v>
       </c>
-      <c r="J1" t="str">
-        <v>hint-3</v>
-      </c>
-      <c r="K1" t="str">
-        <v>hint-3-translation</v>
-      </c>
-      <c r="L1" t="str">
+      <c r="P3" t="str">
         <v>hint-3-type / function</v>
       </c>
-      <c r="M1" t="str">
-        <v>hint-4</v>
-      </c>
-      <c r="N1" t="str">
-        <v>hint-4-translation</v>
-      </c>
-      <c r="O1" t="str">
+      <c r="Q3" t="str">
         <v>hint-4-type / function</v>
       </c>
-      <c r="P1" t="str">
-        <v>hint-5</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>hint-5-translation</v>
-      </c>
-      <c r="R1" t="str">
+      <c r="R3" t="str">
         <v>hint-5-type / function</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="str">
-        <v>work experience</v>
-      </c>
-      <c r="E2" t="str">
-        <v>kinh nghiệm làm việc thực tế</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Keyword</v>
-      </c>
-      <c r="G2" t="str">
-        <v>detailed in my resume</v>
-      </c>
-      <c r="H2" t="str">
-        <v>được trình bày rõ trong hồ sơ</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Ending</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="str">
-        <v>energetic mindset</v>
-      </c>
-      <c r="E3" t="str">
-        <v>tinh thần làm việc năng nổ</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Keyword</v>
-      </c>
-      <c r="G3" t="str">
-        <v>brought to every project</v>
-      </c>
-      <c r="H3" t="str">
-        <v>được mang vào từng dự án</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Ending</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -572,31 +470,31 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="str">
-        <v>accounting function</v>
+        <v>experience</v>
       </c>
       <c r="E4" t="str">
-        <v>nghiệp vụ kế toán tài chính</v>
+        <v>gain</v>
       </c>
       <c r="F4" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>handled with high accuracy</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>được xử lý với độ chuẩn xác cao</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>Ending</v>
+        <v>kinh nghiệm</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>tích lũy</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -608,10 +506,10 @@
         <v/>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="P4" t="str">
         <v/>
@@ -628,31 +526,31 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="str">
-        <v>guide newcomers</v>
+        <v>financial report</v>
       </c>
       <c r="E5" t="str">
-        <v>hướng dẫn nhân viên mới</v>
+        <v>finish</v>
       </c>
       <c r="F5" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>during onboarding week</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>trong tuần đầu hội nhập</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>Ending</v>
+        <v>báo cáo tài chính</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>hoàn thành</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -664,10 +562,10 @@
         <v/>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="P5" t="str">
         <v/>
@@ -684,31 +582,31 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="str">
-        <v>man of the month</v>
+        <v>proactive</v>
       </c>
       <c r="E6" t="str">
-        <v>nhân viên xuất sắc của tháng</v>
+        <v>work</v>
       </c>
       <c r="F6" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>awarded two times consecutively</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>được trao tặng hai lần liên tiếp</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>Ending</v>
+        <v>năng động</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>làm việc</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -720,10 +618,10 @@
         <v/>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>Tính từ · Keyword</v>
       </c>
       <c r="O6" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="P6" t="str">
         <v/>
@@ -740,31 +638,31 @@
         <v>1</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="str">
-        <v>senior student</v>
+        <v>skills</v>
       </c>
       <c r="E7" t="str">
-        <v>sinh viên năm cuối</v>
+        <v>improve</v>
       </c>
       <c r="F7" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>graduating top of class</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>chuẩn bị tốt nghiệp thủ khoa</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>Ending</v>
+        <v>kỹ năng</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>cải thiện</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -776,10 +674,10 @@
         <v/>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O7" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="P7" t="str">
         <v/>
@@ -796,31 +694,31 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="str">
-        <v>daily transactions</v>
+        <v>risk management</v>
       </c>
       <c r="E8" t="str">
-        <v>các giao dịch kế toán hằng ngày</v>
+        <v>careful</v>
       </c>
       <c r="F8" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>reconciled before evening</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>được đối chiếu xong trước buổi tối</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>Ending</v>
+        <v>quản lý rủi ro</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>cẩn thận</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -832,10 +730,10 @@
         <v/>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O8" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="P8" t="str">
         <v/>
@@ -852,31 +750,31 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="str">
-        <v>risk management</v>
+        <v>colleagues</v>
       </c>
       <c r="E9" t="str">
-        <v>nghiệp vụ quản trị rủi ro</v>
+        <v>support</v>
       </c>
       <c r="F9" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>implemented across department</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>được áp dụng khắp phòng ban</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>Ending</v>
+        <v>đồng nghiệp</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>hỗ trợ</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -888,10 +786,10 @@
         <v/>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O9" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="P9" t="str">
         <v/>
@@ -908,31 +806,31 @@
         <v>1</v>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="str">
-        <v>monthly balance sheet</v>
+        <v>job interview</v>
       </c>
       <c r="E10" t="str">
-        <v>bảng cân đối kế toán hàng tháng</v>
+        <v>confident</v>
       </c>
       <c r="F10" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>audited without discrepancies</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>được kiểm toán không sai sót</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>Ending</v>
+        <v>phỏng vấn</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>tự tin</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -944,10 +842,10 @@
         <v/>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O10" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="P10" t="str">
         <v/>
@@ -964,31 +862,31 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="str">
-        <v>top company</v>
+        <v>transactions</v>
       </c>
       <c r="E11" t="str">
-        <v>doanh nghiệp hàng đầu thị trường</v>
+        <v>reconcile</v>
       </c>
       <c r="F11" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>recruited for internship</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>được tuyển vào làm thực tập sinh</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>Ending</v>
+        <v>giao dịch</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>đối soát</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -1000,10 +898,10 @@
         <v/>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O11" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="P11" t="str">
         <v/>
@@ -1020,31 +918,31 @@
         <v>1</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="str">
-        <v>core strengths</v>
+        <v>creative</v>
       </c>
       <c r="E12" t="str">
-        <v>những điểm mạnh then chốt</v>
+        <v>solutions</v>
       </c>
       <c r="F12" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>aligned with job requirements</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>phù hợp hoàn hảo với vị trí ứng tuyển</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>Ending</v>
+        <v>sáng tạo</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>giải pháp</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -1056,10 +954,10 @@
         <v/>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>Tính từ · Keyword</v>
       </c>
       <c r="O12" t="str">
-        <v/>
+        <v>Danh từ · Ending</v>
       </c>
       <c r="P12" t="str">
         <v/>
@@ -1076,31 +974,31 @@
         <v>1</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="str">
-        <v>open-ended questions</v>
+        <v>balance sheet</v>
       </c>
       <c r="E13" t="str">
-        <v>những câu hỏi phỏng vấn mở</v>
+        <v>accurate</v>
       </c>
       <c r="F13" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>answered with calm confidence</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>được trả lời bằng sự tự tin điềm đạm</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>Ending</v>
+        <v>bảng cân đối kế toán</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>chính xác</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -1112,10 +1010,10 @@
         <v/>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O13" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="P13" t="str">
         <v/>
@@ -1132,31 +1030,31 @@
         <v>1</v>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="str">
-        <v>workplace integrity</v>
+        <v>deadline</v>
       </c>
       <c r="E14" t="str">
-        <v>sự chính trực trong công việc</v>
+        <v>meet</v>
       </c>
       <c r="F14" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>valued above all else</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>được coi trọng trên hết mọi thứ</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>Ending</v>
+        <v>hạn chót</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>kịp thời hạn</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -1168,10 +1066,10 @@
         <v/>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O14" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="P14" t="str">
         <v/>
@@ -1188,31 +1086,31 @@
         <v>1</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15" t="str">
-        <v>creative ideas</v>
+        <v>accounting system</v>
       </c>
       <c r="E15" t="str">
-        <v>những sáng kiến đổi mới</v>
+        <v>upgrade</v>
       </c>
       <c r="F15" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>pitched to executive board</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>được trình bày trước ban giám đốc</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>Ending</v>
+        <v>hệ thống kế toán</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>nâng cấp</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -1224,10 +1122,10 @@
         <v/>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O15" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="P15" t="str">
         <v/>
@@ -1244,31 +1142,31 @@
         <v>1</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="str">
-        <v>convince recruiters</v>
+        <v>leadership</v>
       </c>
       <c r="E16" t="str">
-        <v>thuyết phục các nhà tuyển dụng</v>
+        <v>demonstrate</v>
       </c>
       <c r="F16" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>through proven accomplishments</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>thông qua thành tích đã được chứng minh</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>Ending</v>
+        <v>năng lực lãnh đạo</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>thể hiện</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -1280,10 +1178,10 @@
         <v/>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O16" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="P16" t="str">
         <v/>
@@ -1297,49 +1195,49 @@
     </row>
     <row r="17">
       <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17">
         <v>2</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
       <c r="D17" t="str">
-        <v>years of experience</v>
+        <v>audit team</v>
       </c>
       <c r="E17" t="str">
-        <v>nhiều năm kinh nghiệm làm việc</v>
+        <v>coordinate</v>
       </c>
       <c r="F17" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G17" t="str">
-        <v>leveraging solid</v>
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v>tận dụng nền tảng...</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>Logic word</v>
+        <v>đoàn kiểm toán</v>
       </c>
       <c r="J17" t="str">
-        <v>optimized department budget</v>
+        <v>phối hợp</v>
       </c>
       <c r="K17" t="str">
-        <v>tối ưu hóa ngân sách phòng ban</v>
+        <v/>
       </c>
       <c r="L17" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M17" t="str">
         <v/>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O17" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="P17" t="str">
         <v/>
@@ -1353,49 +1251,49 @@
     </row>
     <row r="18">
       <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18">
         <v>2</v>
       </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
       <c r="D18" t="str">
-        <v>company restructuring</v>
+        <v>career path</v>
       </c>
       <c r="E18" t="str">
-        <v>đợt tái cơ cấu doanh nghiệp</v>
+        <v>clear</v>
       </c>
       <c r="F18" t="str">
-        <v>Keyword</v>
+        <v/>
       </c>
       <c r="G18" t="str">
-        <v>following the sudden</v>
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>ngay sau khi diễn ra...</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>Logic word</v>
+        <v>định hướng nghề nghiệp</v>
       </c>
       <c r="J18" t="str">
-        <v>assumed expanded leadership role</v>
+        <v>rõ ràng</v>
       </c>
       <c r="K18" t="str">
-        <v>đảm nhận vai trò lãnh đạo mở rộng</v>
+        <v/>
       </c>
       <c r="L18" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M18" t="str">
         <v/>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O18" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="P18" t="str">
         <v/>
@@ -1412,49 +1310,49 @@
         <v>2</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="str">
-        <v>financial discrepancies</v>
+        <v>tax audit</v>
       </c>
       <c r="E19" t="str">
-        <v>các sai lệch trong sổ sách tài chính</v>
+        <v>before that</v>
       </c>
       <c r="F19" t="str">
-        <v>Keyword</v>
+        <v>prepare</v>
       </c>
       <c r="G19" t="str">
-        <v>in order to eliminate</v>
+        <v/>
       </c>
       <c r="H19" t="str">
-        <v>nhằm mục đích dẹp bỏ...</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>Logic word</v>
+        <v>kiểm toán thuế</v>
       </c>
       <c r="J19" t="str">
-        <v>redesigned verification system</v>
+        <v>trước đó</v>
       </c>
       <c r="K19" t="str">
-        <v>thiết kế lại hệ thống đối soát dữ liệu</v>
+        <v>chuẩn bị kỹ</v>
       </c>
       <c r="L19" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O19" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P19" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="Q19" t="str">
         <v/>
@@ -1468,49 +1366,49 @@
         <v>2</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
       <c r="D20" t="str">
-        <v>tight deadline pressure</v>
+        <v>financial data</v>
       </c>
       <c r="E20" t="str">
-        <v>áp lực thời hạn bàn giao gấp gáp</v>
+        <v>therefore</v>
       </c>
       <c r="F20" t="str">
-        <v>Keyword</v>
+        <v>reliable</v>
       </c>
       <c r="G20" t="str">
-        <v>despite working under</v>
+        <v/>
       </c>
       <c r="H20" t="str">
-        <v>mặc dù luôn phải chịu...</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>Logic word</v>
+        <v>dữ liệu tài chính</v>
       </c>
       <c r="J20" t="str">
-        <v>delivered quarterly report flawlessly</v>
+        <v>do đó</v>
       </c>
       <c r="K20" t="str">
-        <v>hoàn thành báo cáo quý không tì vết</v>
+        <v>đáng tin cậy</v>
       </c>
       <c r="L20" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M20" t="str">
         <v/>
       </c>
       <c r="N20" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O20" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="Q20" t="str">
         <v/>
@@ -1524,49 +1422,49 @@
         <v>2</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
       <c r="D21" t="str">
-        <v>training new recruits</v>
+        <v>team performance</v>
       </c>
       <c r="E21" t="str">
-        <v>việc đào tạo nhân sự mới vào</v>
+        <v>in addition</v>
       </c>
       <c r="F21" t="str">
-        <v>Keyword</v>
+        <v>exceed</v>
       </c>
       <c r="G21" t="str">
-        <v>being responsible for</v>
+        <v/>
       </c>
       <c r="H21" t="str">
-        <v>chịu trách nhiệm chính trong việc...</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v>Logic word</v>
+        <v>hiệu suất nhóm</v>
       </c>
       <c r="J21" t="str">
-        <v>boosted team productivity greatly</v>
+        <v>hơn nữa</v>
       </c>
       <c r="K21" t="str">
-        <v>nâng cao đáng kể hiệu suất toàn đội ngũ</v>
+        <v>vượt chỉ tiêu</v>
       </c>
       <c r="L21" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M21" t="str">
         <v/>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O21" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P21" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="Q21" t="str">
         <v/>
@@ -1580,49 +1478,49 @@
         <v>2</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" t="str">
-        <v>e-commerce campaign</v>
+        <v>cash flow</v>
       </c>
       <c r="E22" t="str">
-        <v>chiến dịch bán hàng thương mại điện tử</v>
+        <v>meanwhile</v>
       </c>
       <c r="F22" t="str">
-        <v>Keyword</v>
+        <v>healthy</v>
       </c>
       <c r="G22" t="str">
-        <v>while managing the</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v>trong lúc điều hành...</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v>Logic word</v>
+        <v>dòng tiền</v>
       </c>
       <c r="J22" t="str">
-        <v>doubled monthly sales revenue</v>
+        <v>đồng thời</v>
       </c>
       <c r="K22" t="str">
-        <v>tăng gấp đôi doanh số bán hàng tháng</v>
+        <v>dồi dào lành mạnh</v>
       </c>
       <c r="L22" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M22" t="str">
         <v/>
       </c>
       <c r="N22" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O22" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="Q22" t="str">
         <v/>
@@ -1636,49 +1534,49 @@
         <v>2</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C23">
         <v>3</v>
       </c>
       <c r="D23" t="str">
-        <v>academic research honors</v>
+        <v>data discrepancy</v>
       </c>
       <c r="E23" t="str">
-        <v>giải thưởng nghiên cứu học thuật</v>
+        <v>however</v>
       </c>
       <c r="F23" t="str">
-        <v>Keyword</v>
+        <v>resolved</v>
       </c>
       <c r="G23" t="str">
-        <v>as a result of winning</v>
+        <v/>
       </c>
       <c r="H23" t="str">
-        <v>nhờ đạt được...</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v>Logic word</v>
+        <v>chênh lệch số liệu</v>
       </c>
       <c r="J23" t="str">
-        <v>secured full scholarship grant</v>
+        <v>tuy nhiên</v>
       </c>
       <c r="K23" t="str">
-        <v>nhận được suất học bổng toàn phần</v>
+        <v>được xử lý</v>
       </c>
       <c r="L23" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M23" t="str">
         <v/>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O23" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P23" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="Q23" t="str">
         <v/>
@@ -1692,49 +1590,49 @@
         <v>2</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
       <c r="D24" t="str">
-        <v>clearance sales campaign</v>
+        <v>job promotion</v>
       </c>
       <c r="E24" t="str">
-        <v>chiến dịch xả hàng tồn kho lớn</v>
+        <v>as long as</v>
       </c>
       <c r="F24" t="str">
-        <v>Keyword</v>
+        <v>dedicated</v>
       </c>
       <c r="G24" t="str">
-        <v>specifically focusing on</v>
+        <v/>
       </c>
       <c r="H24" t="str">
-        <v>tập trung mũi nhọn vào...</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v>Logic word</v>
+        <v>thăng tiến công việc</v>
       </c>
       <c r="J24" t="str">
-        <v>liquidated surplus inventory fast</v>
+        <v>miễn là</v>
       </c>
       <c r="K24" t="str">
-        <v>giải phóng sạch lượng hàng tồn nhanh chóng</v>
+        <v>tận tụy</v>
       </c>
       <c r="L24" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M24" t="str">
         <v/>
       </c>
       <c r="N24" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O24" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P24" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="Q24" t="str">
         <v/>
@@ -1748,49 +1646,49 @@
         <v>2</v>
       </c>
       <c r="B25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25" t="str">
-        <v>unrelated interview questions</v>
+        <v>annual budget</v>
       </c>
       <c r="E25" t="str">
-        <v>những câu hỏi phỏng vấn lạc đề</v>
+        <v>next</v>
       </c>
       <c r="F25" t="str">
-        <v>Keyword</v>
+        <v>approved</v>
       </c>
       <c r="G25" t="str">
-        <v>when confronted with</v>
+        <v/>
       </c>
       <c r="H25" t="str">
-        <v>khi bất ngờ đối mặt với...</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v>Logic word</v>
+        <v>ngân sách năm</v>
       </c>
       <c r="J25" t="str">
-        <v>steered back to core skills</v>
+        <v>tiếp theo</v>
       </c>
       <c r="K25" t="str">
-        <v>khéo léo dẫn dắt về kỹ năng trọng tâm</v>
+        <v>được thông qua</v>
       </c>
       <c r="L25" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M25" t="str">
         <v/>
       </c>
       <c r="N25" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O25" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P25" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="Q25" t="str">
         <v/>
@@ -1804,49 +1702,49 @@
         <v>2</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C26">
         <v>3</v>
       </c>
       <c r="D26" t="str">
-        <v>interpersonal team conflict</v>
+        <v>internal control</v>
       </c>
       <c r="E26" t="str">
-        <v>bất đồng quan điểm giữa đồng nghiệp</v>
+        <v>otherwise</v>
       </c>
       <c r="F26" t="str">
-        <v>Keyword</v>
+        <v>risky</v>
       </c>
       <c r="G26" t="str">
-        <v>stepped in to resolve</v>
+        <v/>
       </c>
       <c r="H26" t="str">
-        <v>chủ động đứng ra hòa giải...</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v>Logic word</v>
+        <v>kiểm soát nội bộ</v>
       </c>
       <c r="J26" t="str">
-        <v>restored productive workspace harmony</v>
+        <v>nếu không</v>
       </c>
       <c r="K26" t="str">
-        <v>lấy lại bầu không khí làm việc hiệu quả</v>
+        <v>rủi ro cao</v>
       </c>
       <c r="L26" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O26" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P26" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="Q26" t="str">
         <v/>
@@ -1860,49 +1758,49 @@
         <v>2</v>
       </c>
       <c r="B27">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C27">
         <v>3</v>
       </c>
       <c r="D27" t="str">
-        <v>cross-department collaboration</v>
+        <v>professional growth</v>
       </c>
       <c r="E27" t="str">
-        <v>sự phối hợp giữa các phòng ban</v>
+        <v>if</v>
       </c>
       <c r="F27" t="str">
-        <v>Keyword</v>
+        <v>persistent</v>
       </c>
       <c r="G27" t="str">
-        <v>by actively promoting</v>
+        <v/>
       </c>
       <c r="H27" t="str">
-        <v>bằng cách thúc đẩy mạnh mẽ...</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v>Logic word</v>
+        <v>phát triển chuyên môn</v>
       </c>
       <c r="J27" t="str">
-        <v>accelerated product launch timeline</v>
+        <v>nếu</v>
       </c>
       <c r="K27" t="str">
-        <v>đẩy nhanh tiến độ tung sản phẩm mới</v>
+        <v>kiên trì</v>
       </c>
       <c r="L27" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M27" t="str">
         <v/>
       </c>
       <c r="N27" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O27" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P27" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="Q27" t="str">
         <v/>
@@ -1916,49 +1814,49 @@
         <v>2</v>
       </c>
       <c r="B28">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C28">
         <v>3</v>
       </c>
       <c r="D28" t="str">
-        <v>unexpected budget cuts</v>
+        <v>accounting books</v>
       </c>
       <c r="E28" t="str">
-        <v>việc cắt giảm ngân sách bất ngờ</v>
+        <v>eventually</v>
       </c>
       <c r="F28" t="str">
-        <v>Keyword</v>
+        <v>transparent</v>
       </c>
       <c r="G28" t="str">
-        <v>adapting quickly to</v>
+        <v/>
       </c>
       <c r="H28" t="str">
-        <v>nhanh chóng thích nghi trước...</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v>Logic word</v>
+        <v>sổ sách kế toán</v>
       </c>
       <c r="J28" t="str">
-        <v>automated manual accounting tasks</v>
+        <v>sau cùng</v>
       </c>
       <c r="K28" t="str">
-        <v>tự động hóa các thao tác kế toán thủ công</v>
+        <v>minh bạch</v>
       </c>
       <c r="L28" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M28" t="str">
         <v/>
       </c>
       <c r="N28" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O28" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="Q28" t="str">
         <v/>
@@ -1972,49 +1870,49 @@
         <v>2</v>
       </c>
       <c r="B29">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="D29" t="str">
-        <v>demanding client expectations</v>
+        <v>market analysis</v>
       </c>
       <c r="E29" t="str">
-        <v>kỳ vọng khắt khe từ phía khách hàng</v>
+        <v>in other words</v>
       </c>
       <c r="F29" t="str">
-        <v>Keyword</v>
+        <v>strategic</v>
       </c>
       <c r="G29" t="str">
-        <v>in order to exceed</v>
+        <v/>
       </c>
       <c r="H29" t="str">
-        <v>với quyết tâm vượt qua...</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v>Logic word</v>
+        <v>phân tích thị trường</v>
       </c>
       <c r="J29" t="str">
-        <v>provided continuous project updates</v>
+        <v>nói cách khác</v>
       </c>
       <c r="K29" t="str">
-        <v>liên tục báo cáo tiến độ minh bạch</v>
+        <v>có tính chiến lược</v>
       </c>
       <c r="L29" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M29" t="str">
         <v/>
       </c>
       <c r="N29" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O29" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P29" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="Q29" t="str">
         <v/>
@@ -2028,49 +1926,49 @@
         <v>2</v>
       </c>
       <c r="B30">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="str">
-        <v>new software rollout</v>
+        <v>heavy workload</v>
       </c>
       <c r="E30" t="str">
-        <v>việc triển khai phần mềm nghiệp vụ mới</v>
+        <v>nevertheless</v>
       </c>
       <c r="F30" t="str">
-        <v>Keyword</v>
+        <v>manageable</v>
       </c>
       <c r="G30" t="str">
-        <v>prior to executing</v>
+        <v/>
       </c>
       <c r="H30" t="str">
-        <v>trước thời điểm đưa vào vận hành...</v>
+        <v/>
       </c>
       <c r="I30" t="str">
-        <v>Logic word</v>
+        <v>khối lượng công việc lớn</v>
       </c>
       <c r="J30" t="str">
-        <v>conducted hands-on user training</v>
+        <v>dù vậy</v>
       </c>
       <c r="K30" t="str">
-        <v>trực tiếp hướng dẫn thao tác cho người dùng</v>
+        <v>xoay xở ổn</v>
       </c>
       <c r="L30" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M30" t="str">
         <v/>
       </c>
       <c r="N30" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O30" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P30" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="Q30" t="str">
         <v/>
@@ -2084,49 +1982,49 @@
         <v>2</v>
       </c>
       <c r="B31">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
       <c r="D31" t="str">
-        <v>interview anxiety jitters</v>
+        <v>software training</v>
       </c>
       <c r="E31" t="str">
-        <v>cảm giác hồi hộp lo lắng khi phỏng vấn</v>
+        <v>for example</v>
       </c>
       <c r="F31" t="str">
-        <v>Keyword</v>
+        <v>productive</v>
       </c>
       <c r="G31" t="str">
-        <v>managed to overcome</v>
+        <v/>
       </c>
       <c r="H31" t="str">
-        <v>đã hoàn toàn chiến thắng...</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v>Logic word</v>
+        <v>đào tạo phần mềm</v>
       </c>
       <c r="J31" t="str">
-        <v>delivered convincing personal pitch</v>
+        <v>ví dụ</v>
       </c>
       <c r="K31" t="str">
-        <v>trình bày bài giới thiệu bản thân thuyết phục</v>
+        <v>năng suất</v>
       </c>
       <c r="L31" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
       <c r="M31" t="str">
         <v/>
       </c>
       <c r="N31" t="str">
-        <v/>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O31" t="str">
-        <v/>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P31" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="Q31" t="str">
         <v/>
@@ -2137,52 +2035,52 @@
     </row>
     <row r="32">
       <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32">
+        <v>14</v>
+      </c>
+      <c r="C32">
         <v>3</v>
       </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32">
-        <v>4</v>
-      </c>
       <c r="D32" t="str">
-        <v>accounting function</v>
+        <v>client relationship</v>
       </c>
       <c r="E32" t="str">
-        <v>chức năng kế toán doanh nghiệp</v>
+        <v>then</v>
       </c>
       <c r="F32" t="str">
-        <v>Keyword</v>
+        <v>strengthen</v>
       </c>
       <c r="G32" t="str">
-        <v>overseeing the entire</v>
+        <v/>
       </c>
       <c r="H32" t="str">
-        <v>chịu trách nhiệm bao quát toàn bộ...</v>
+        <v/>
       </c>
       <c r="I32" t="str">
-        <v>Logic word</v>
+        <v>quan hệ khách hàng</v>
       </c>
       <c r="J32" t="str">
-        <v>complex corporate ledger</v>
+        <v>sau đó</v>
       </c>
       <c r="K32" t="str">
-        <v>hệ thống sổ cái doanh nghiệp phức tạp</v>
+        <v>củng cố vững chắc</v>
       </c>
       <c r="L32" t="str">
-        <v>Fancy word</v>
+        <v/>
       </c>
       <c r="M32" t="str">
-        <v>eliminated costly financial errors</v>
+        <v/>
       </c>
       <c r="N32" t="str">
-        <v>loại bỏ sạch các sai sót tài chính tốn kém</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O32" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P32" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="Q32" t="str">
         <v/>
@@ -2193,52 +2091,52 @@
     </row>
     <row r="33">
       <c r="A33">
+        <v>2</v>
+      </c>
+      <c r="B33">
+        <v>15</v>
+      </c>
+      <c r="C33">
         <v>3</v>
       </c>
-      <c r="B33">
-        <v>2</v>
-      </c>
-      <c r="C33">
-        <v>4</v>
-      </c>
       <c r="D33" t="str">
-        <v>mentoring junior staff</v>
+        <v>project milestone</v>
       </c>
       <c r="E33" t="str">
-        <v>việc dẫn dắt kèm cặp nhân viên mới</v>
+        <v>besides</v>
       </c>
       <c r="F33" t="str">
-        <v>Keyword</v>
+        <v>completed</v>
       </c>
       <c r="G33" t="str">
-        <v>dedicatedly committing to</v>
+        <v/>
       </c>
       <c r="H33" t="str">
-        <v>tận tâm cống hiến cho...</v>
+        <v/>
       </c>
       <c r="I33" t="str">
-        <v>Logic word</v>
+        <v>mốc tiến độ dự án</v>
       </c>
       <c r="J33" t="str">
-        <v>structured onboarding curriculum</v>
+        <v>ngoài ra</v>
       </c>
       <c r="K33" t="str">
-        <v>giáo trình đào tạo hội nhập bài bản</v>
+        <v>hoàn tất</v>
       </c>
       <c r="L33" t="str">
-        <v>Fancy word</v>
+        <v/>
       </c>
       <c r="M33" t="str">
-        <v>received man of the month award</v>
+        <v/>
       </c>
       <c r="N33" t="str">
-        <v>được nhận danh hiệu nhân viên của tháng</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O33" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P33" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="Q33" t="str">
         <v/>
@@ -2252,52 +2150,52 @@
         <v>3</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34">
         <v>4</v>
       </c>
       <c r="D34" t="str">
-        <v>promotional sales campaign</v>
+        <v>risk assessment</v>
       </c>
       <c r="E34" t="str">
-        <v>chiến dịch khuyến mãi kích cầu</v>
+        <v>while</v>
       </c>
       <c r="F34" t="str">
-        <v>Keyword</v>
+        <v>red flag</v>
       </c>
       <c r="G34" t="str">
-        <v>strategically designing a</v>
+        <v>investigate</v>
       </c>
       <c r="H34" t="str">
-        <v>lên chiến lược thiết kế một...</v>
+        <v/>
       </c>
       <c r="I34" t="str">
-        <v>Logic word</v>
+        <v>đánh giá rủi ro</v>
       </c>
       <c r="J34" t="str">
-        <v>viral like-farming promotion</v>
+        <v>trong khi</v>
       </c>
       <c r="K34" t="str">
-        <v>chiến dịch tương tác lan tỏa mạnh mẽ</v>
+        <v>dấu hiệu cảnh báo</v>
       </c>
       <c r="L34" t="str">
-        <v>Fancy word</v>
+        <v>điều tra kỹ</v>
       </c>
       <c r="M34" t="str">
-        <v>drove massive online conversions</v>
+        <v/>
       </c>
       <c r="N34" t="str">
-        <v>kéo về lượng đơn hàng trực tuyến khổng lồ</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O34" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P34" t="str">
-        <v/>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q34" t="str">
-        <v/>
+        <v>Động từ · Ending</v>
       </c>
       <c r="R34" t="str">
         <v/>
@@ -2308,52 +2206,52 @@
         <v>3</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C35">
         <v>4</v>
       </c>
       <c r="D35" t="str">
-        <v>rigorous audit preparation</v>
+        <v>audit season</v>
       </c>
       <c r="E35" t="str">
-        <v>công tác chuẩn bị kiểm toán gắt gao</v>
+        <v>however</v>
       </c>
       <c r="F35" t="str">
-        <v>Keyword</v>
+        <v>lifeline</v>
       </c>
       <c r="G35" t="str">
-        <v>meticulously completing the</v>
+        <v>supportive</v>
       </c>
       <c r="H35" t="str">
-        <v>hoàn thành tỉ mỉ từng hạng mục của...</v>
+        <v/>
       </c>
       <c r="I35" t="str">
-        <v>Logic word</v>
+        <v>mùa kiểm toán</v>
       </c>
       <c r="J35" t="str">
-        <v>monthly balance sheet</v>
+        <v>tuy nhiên</v>
       </c>
       <c r="K35" t="str">
-        <v>bảng cân đối kế toán hàng tháng</v>
+        <v>phao cứu cánh</v>
       </c>
       <c r="L35" t="str">
-        <v>Fancy word</v>
+        <v>tương trợ đắc lực</v>
       </c>
       <c r="M35" t="str">
-        <v>earned praise from senior partners</v>
+        <v/>
       </c>
       <c r="N35" t="str">
-        <v>được các đối tác cấp cao hết lời khen ngợi</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O35" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P35" t="str">
-        <v/>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q35" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R35" t="str">
         <v/>
@@ -2364,52 +2262,52 @@
         <v>3</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C36">
         <v>4</v>
       </c>
       <c r="D36" t="str">
-        <v>senior student leader</v>
+        <v>Why accounting</v>
       </c>
       <c r="E36" t="str">
-        <v>thủ lĩnh sinh viên năm cuối</v>
+        <v>finally</v>
       </c>
       <c r="F36" t="str">
-        <v>Keyword</v>
+        <v>stepping stone</v>
       </c>
       <c r="G36" t="str">
-        <v>excelling consistently as a</v>
+        <v>rewarding</v>
       </c>
       <c r="H36" t="str">
-        <v>luôn giữ vững phong độ xuất sắc của một...</v>
+        <v/>
       </c>
       <c r="I36" t="str">
-        <v>Logic word</v>
+        <v>Tại sao chọn kế toán</v>
       </c>
       <c r="J36" t="str">
-        <v>top economics university scholar</v>
+        <v>sau cùng</v>
       </c>
       <c r="K36" t="str">
-        <v>sinh viên ưu tú trường đại học kinh tế</v>
+        <v>bước đệm vững chắc</v>
       </c>
       <c r="L36" t="str">
-        <v>Fancy word</v>
+        <v>xứng đáng</v>
       </c>
       <c r="M36" t="str">
-        <v>transitioned smoothly into full-time role</v>
+        <v/>
       </c>
       <c r="N36" t="str">
-        <v>chuyển tiếp suôn sẻ sang vị trí chính thức</v>
+        <v>Cụm nghi vấn · WH word</v>
       </c>
       <c r="O36" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P36" t="str">
-        <v/>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q36" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R36" t="str">
         <v/>
@@ -2420,52 +2318,52 @@
         <v>3</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C37">
         <v>4</v>
       </c>
       <c r="D37" t="str">
-        <v>unforeseen corporate restructuring</v>
+        <v>financial discrepancy</v>
       </c>
       <c r="E37" t="str">
-        <v>việc tái cấu trúc doanh nghiệp bất ngờ</v>
+        <v>therefore</v>
       </c>
       <c r="F37" t="str">
-        <v>Keyword</v>
+        <v>wake-up call</v>
       </c>
       <c r="G37" t="str">
-        <v>successfully weathering the</v>
+        <v>corrected</v>
       </c>
       <c r="H37" t="str">
-        <v>vượt qua trọn vẹn giai đoạn...</v>
+        <v/>
       </c>
       <c r="I37" t="str">
-        <v>Logic word</v>
+        <v>bất thường tài chính</v>
       </c>
       <c r="J37" t="str">
-        <v>turbulent managerial transition</v>
+        <v>do đó</v>
       </c>
       <c r="K37" t="str">
-        <v>chuyển giao bộ máy quản lý đầy biến động</v>
+        <v>hồi chuông cảnh tỉnh</v>
       </c>
       <c r="L37" t="str">
-        <v>Fancy word</v>
+        <v>đã sửa chữa</v>
       </c>
       <c r="M37" t="str">
-        <v>retained key client accounts intact</v>
+        <v/>
       </c>
       <c r="N37" t="str">
-        <v>giữ vững các hợp đồng khách hàng trọng điểm</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O37" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P37" t="str">
-        <v/>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q37" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R37" t="str">
         <v/>
@@ -2476,52 +2374,52 @@
         <v>3</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>4</v>
       </c>
       <c r="D38" t="str">
-        <v>uncompromising workplace integrity</v>
+        <v>balance sheet</v>
       </c>
       <c r="E38" t="str">
-        <v>tính chính trực tuyệt đối trong công sở</v>
+        <v>in contrast</v>
       </c>
       <c r="F38" t="str">
-        <v>Keyword</v>
+        <v>rock solid</v>
       </c>
       <c r="G38" t="str">
-        <v>firmly upholding our</v>
+        <v>accurate</v>
       </c>
       <c r="H38" t="str">
-        <v>luôn kiên định giữ vững...</v>
+        <v/>
       </c>
       <c r="I38" t="str">
-        <v>Logic word</v>
+        <v>bảng cân đối kế toán</v>
       </c>
       <c r="J38" t="str">
-        <v>transparent governance standards</v>
+        <v>ngược lại</v>
       </c>
       <c r="K38" t="str">
-        <v>những chuẩn mực quản trị minh bạch</v>
+        <v>vững như bàn thạch</v>
       </c>
       <c r="L38" t="str">
-        <v>Fancy word</v>
+        <v>chuẩn xác</v>
       </c>
       <c r="M38" t="str">
-        <v>earned trust from executive directors</v>
+        <v/>
       </c>
       <c r="N38" t="str">
-        <v>tạo dựng niềm tin vững chắc từ hội đồng quản trị</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O38" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P38" t="str">
-        <v/>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q38" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R38" t="str">
         <v/>
@@ -2532,52 +2430,52 @@
         <v>3</v>
       </c>
       <c r="B39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C39">
         <v>4</v>
       </c>
       <c r="D39" t="str">
-        <v>behavioral interview pitch</v>
+        <v>Which strength</v>
       </c>
       <c r="E39" t="str">
-        <v>phần trả lời phỏng vấn hành vi</v>
+        <v>otherwise</v>
       </c>
       <c r="F39" t="str">
-        <v>Keyword</v>
+        <v>trump card</v>
       </c>
       <c r="G39" t="str">
-        <v>delivering an articulate</v>
+        <v>outstanding</v>
       </c>
       <c r="H39" t="str">
-        <v>trình bày một cách mạch lạc trong...</v>
+        <v/>
       </c>
       <c r="I39" t="str">
-        <v>Logic word</v>
+        <v>Điểm mạnh nào</v>
       </c>
       <c r="J39" t="str">
-        <v>compelling professional narrative</v>
+        <v>nếu không</v>
       </c>
       <c r="K39" t="str">
-        <v>câu chuyện phát triển sự nghiệp đầy thuyết phục</v>
+        <v>con bài chiến lược</v>
       </c>
       <c r="L39" t="str">
-        <v>Fancy word</v>
+        <v>vượt trội</v>
       </c>
       <c r="M39" t="str">
-        <v>impressed recruitment committee deeply</v>
+        <v/>
       </c>
       <c r="N39" t="str">
-        <v>gây ấn tượng sâu sắc với hội đồng tuyển dụng</v>
+        <v>Cụm nghi vấn · WH word</v>
       </c>
       <c r="O39" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P39" t="str">
-        <v/>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q39" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R39" t="str">
         <v/>
@@ -2588,52 +2486,52 @@
         <v>3</v>
       </c>
       <c r="B40">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C40">
         <v>4</v>
       </c>
       <c r="D40" t="str">
-        <v>cross-functional team synergy</v>
+        <v>budget deficit</v>
       </c>
       <c r="E40" t="str">
-        <v>sức mạnh gắn kết liên phòng ban</v>
+        <v>nevertheless</v>
       </c>
       <c r="F40" t="str">
-        <v>Keyword</v>
+        <v>game plan</v>
       </c>
       <c r="G40" t="str">
-        <v>actively fostering strong</v>
+        <v>solved</v>
       </c>
       <c r="H40" t="str">
-        <v>tích cực gây dựng và nuôi dưỡng...</v>
+        <v/>
       </c>
       <c r="I40" t="str">
-        <v>Logic word</v>
+        <v>thâm hụt ngân sách</v>
       </c>
       <c r="J40" t="str">
-        <v>harmonious workplace collaboration</v>
+        <v>dù vậy</v>
       </c>
       <c r="K40" t="str">
-        <v>sự cộng tác hài hòa nơi công sở</v>
+        <v>chiến lược bài bản</v>
       </c>
       <c r="L40" t="str">
-        <v>Fancy word</v>
+        <v>được tháo gỡ</v>
       </c>
       <c r="M40" t="str">
-        <v>surpassed annual departmental goals</v>
+        <v/>
       </c>
       <c r="N40" t="str">
-        <v>hoàn thành vượt mức chỉ tiêu năm của phòng</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O40" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P40" t="str">
-        <v/>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q40" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R40" t="str">
         <v/>
@@ -2644,52 +2542,52 @@
         <v>3</v>
       </c>
       <c r="B41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C41">
         <v>4</v>
       </c>
       <c r="D41" t="str">
-        <v>high-stakes client negotiation</v>
+        <v>data integrity</v>
       </c>
       <c r="E41" t="str">
-        <v>cuộc đàm phán hợp đồng cân não</v>
+        <v>as long as</v>
       </c>
       <c r="F41" t="str">
-        <v>Keyword</v>
+        <v>cornerstone</v>
       </c>
       <c r="G41" t="str">
-        <v>leading the crucial</v>
+        <v>intact</v>
       </c>
       <c r="H41" t="str">
-        <v>dẫn dắt trực tiếp phiên...</v>
+        <v/>
       </c>
       <c r="I41" t="str">
-        <v>Logic word</v>
+        <v>tính toàn vẹn dữ liệu</v>
       </c>
       <c r="J41" t="str">
-        <v>strategic enterprise partnership</v>
+        <v>miễn là</v>
       </c>
       <c r="K41" t="str">
-        <v>hợp tác chiến lược cấp doanh nghiệp</v>
+        <v>hòn đá tảng</v>
       </c>
       <c r="L41" t="str">
-        <v>Fancy word</v>
+        <v>nguyên vẹn</v>
       </c>
       <c r="M41" t="str">
-        <v>secured multi-year service contract</v>
+        <v/>
       </c>
       <c r="N41" t="str">
-        <v>ký kết thành công hợp đồng dài hạn nhiều năm</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O41" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P41" t="str">
-        <v/>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q41" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R41" t="str">
         <v/>
@@ -2700,52 +2598,52 @@
         <v>3</v>
       </c>
       <c r="B42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C42">
         <v>4</v>
       </c>
       <c r="D42" t="str">
-        <v>proactive workflow automation</v>
+        <v>How much value</v>
       </c>
       <c r="E42" t="str">
-        <v>chủ động tự động hóa luồng công việc</v>
+        <v>if</v>
       </c>
       <c r="F42" t="str">
-        <v>Keyword</v>
+        <v>win-win</v>
       </c>
       <c r="G42" t="str">
-        <v>spearheading modern</v>
+        <v>measurable</v>
       </c>
       <c r="H42" t="str">
-        <v>tiên phong dẫn dắt quá trình...</v>
+        <v/>
       </c>
       <c r="I42" t="str">
-        <v>Logic word</v>
+        <v>Đem lại bao nhiêu giá trị</v>
       </c>
       <c r="J42" t="str">
-        <v>innovative software integration</v>
+        <v>nếu</v>
       </c>
       <c r="K42" t="str">
-        <v>tích hợp phần mềm đổi mới công nghệ</v>
+        <v>đôi bên cùng có lợi</v>
       </c>
       <c r="L42" t="str">
-        <v>Fancy word</v>
+        <v>đo lường được</v>
       </c>
       <c r="M42" t="str">
-        <v>slashed transaction processing time</v>
+        <v/>
       </c>
       <c r="N42" t="str">
-        <v>cắt giảm một nửa thời gian xử lý giao dịch</v>
+        <v>Cụm nghi vấn · WH word</v>
       </c>
       <c r="O42" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P42" t="str">
-        <v/>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q42" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R42" t="str">
         <v/>
@@ -2756,52 +2654,52 @@
         <v>3</v>
       </c>
       <c r="B43">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C43">
         <v>4</v>
       </c>
       <c r="D43" t="str">
-        <v>challenging open-ended questions</v>
+        <v>executive pitch</v>
       </c>
       <c r="E43" t="str">
-        <v>những câu hỏi mở đầy thử thách</v>
+        <v>before that</v>
       </c>
       <c r="F43" t="str">
-        <v>Keyword</v>
+        <v>dry run</v>
       </c>
       <c r="G43" t="str">
-        <v>deftly unpacking each</v>
+        <v>persuasive</v>
       </c>
       <c r="H43" t="str">
-        <v>khéo léo bóc tách và phân tích từng...</v>
+        <v/>
       </c>
       <c r="I43" t="str">
-        <v>Logic word</v>
+        <v>bài thuyết trình ban giám đốc</v>
       </c>
       <c r="J43" t="str">
-        <v>intricate scenario dilemma</v>
+        <v>trước đó</v>
       </c>
       <c r="K43" t="str">
-        <v>tình huống nghiệp vụ hóc búa</v>
+        <v>buổi tập dượt kỹ</v>
       </c>
       <c r="L43" t="str">
-        <v>Fancy word</v>
+        <v>thuyết phục</v>
       </c>
       <c r="M43" t="str">
-        <v>convinced interview panel decisively</v>
+        <v/>
       </c>
       <c r="N43" t="str">
-        <v>thuyết phục hoàn toàn các vị giám khảo</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O43" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P43" t="str">
-        <v/>
+        <v>Cụm gợi hình · Fancy word</v>
       </c>
       <c r="Q43" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R43" t="str">
         <v/>
@@ -2812,52 +2710,52 @@
         <v>3</v>
       </c>
       <c r="B44">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C44">
         <v>4</v>
       </c>
       <c r="D44" t="str">
-        <v>rapid market downturn</v>
+        <v>system bottleneck</v>
       </c>
       <c r="E44" t="str">
-        <v>thời kỳ thị trường suy thoái nhanh</v>
+        <v>in addition</v>
       </c>
       <c r="F44" t="str">
-        <v>Keyword</v>
+        <v>silver bullet</v>
       </c>
       <c r="G44" t="str">
-        <v>remaining agile during</v>
+        <v>streamlined</v>
       </c>
       <c r="H44" t="str">
-        <v>giữ vững sự linh hoạt bén nhạy giữa...</v>
+        <v/>
       </c>
       <c r="I44" t="str">
-        <v>Logic word</v>
+        <v>nút thắt cổ chai</v>
       </c>
       <c r="J44" t="str">
-        <v>severe industry headwind</v>
+        <v>hơn nữa</v>
       </c>
       <c r="K44" t="str">
-        <v>những cơn sóng gió ngành khốc liệt</v>
+        <v>phương thuốc đặc trị</v>
       </c>
       <c r="L44" t="str">
-        <v>Fancy word</v>
+        <v>tinh gọn</v>
       </c>
       <c r="M44" t="str">
-        <v>maintained positive operating margins</v>
+        <v/>
       </c>
       <c r="N44" t="str">
-        <v>duy trì tốt biên lợi nhuận hoạt động dương</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O44" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P44" t="str">
-        <v/>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q44" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R44" t="str">
         <v/>
@@ -2868,52 +2766,52 @@
         <v>3</v>
       </c>
       <c r="B45">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C45">
         <v>4</v>
       </c>
       <c r="D45" t="str">
-        <v>dynamic project management</v>
+        <v>probation period</v>
       </c>
       <c r="E45" t="str">
-        <v>năng lực điều phối dự án linh hoạt</v>
+        <v>next</v>
       </c>
       <c r="F45" t="str">
-        <v>Keyword</v>
+        <v>acid test</v>
       </c>
       <c r="G45" t="str">
-        <v>effectively utilizing modern</v>
+        <v>passed</v>
       </c>
       <c r="H45" t="str">
-        <v>vận dụng hiệu quả những...</v>
+        <v/>
       </c>
       <c r="I45" t="str">
-        <v>Logic word</v>
+        <v>giai đoạn thử việc</v>
       </c>
       <c r="J45" t="str">
-        <v>agile delivery methodologies</v>
+        <v>tiếp theo</v>
       </c>
       <c r="K45" t="str">
-        <v>phương pháp quản trị dự án tinh gọn</v>
+        <v>phép thử thực tế</v>
       </c>
       <c r="L45" t="str">
-        <v>Fancy word</v>
+        <v>vượt qua xuất sắc</v>
       </c>
       <c r="M45" t="str">
-        <v>delivered milestone ahead of schedule</v>
+        <v/>
       </c>
       <c r="N45" t="str">
-        <v>bàn giao cột mốc công việc trước tiến độ</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O45" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P45" t="str">
-        <v/>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q45" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R45" t="str">
         <v/>
@@ -2924,52 +2822,52 @@
         <v>3</v>
       </c>
       <c r="B46">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C46">
         <v>4</v>
       </c>
       <c r="D46" t="str">
-        <v>long-term career roadmap</v>
+        <v>Where to improve</v>
       </c>
       <c r="E46" t="str">
-        <v>lộ trình phát triển sự nghiệp lâu dài</v>
+        <v>then</v>
       </c>
       <c r="F46" t="str">
-        <v>Keyword</v>
+        <v>learning curve</v>
       </c>
       <c r="G46" t="str">
-        <v>clearly presenting a</v>
+        <v>accelerated</v>
       </c>
       <c r="H46" t="str">
-        <v>trình bày rõ ràng và mạch lạc một...</v>
+        <v/>
       </c>
       <c r="I46" t="str">
-        <v>Logic word</v>
+        <v>Nên cải thiện mặt nào</v>
       </c>
       <c r="J46" t="str">
-        <v>purposeful leadership trajectory</v>
+        <v>sau đó</v>
       </c>
       <c r="K46" t="str">
-        <v>định hướng phát triển năng lực lãnh đạo</v>
+        <v>quá trình tiếp thu</v>
       </c>
       <c r="L46" t="str">
-        <v>Fancy word</v>
+        <v>được đẩy nhanh</v>
       </c>
       <c r="M46" t="str">
-        <v>demonstrated strong company commitment</v>
+        <v/>
       </c>
       <c r="N46" t="str">
-        <v>khẳng định cam kết gắn bó lâu dài cùng công ty</v>
+        <v>Cụm nghi vấn · WH word</v>
       </c>
       <c r="O46" t="str">
-        <v>Ending</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P46" t="str">
-        <v/>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q46" t="str">
-        <v/>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R46" t="str">
         <v/>
@@ -2977,114 +2875,114 @@
     </row>
     <row r="47">
       <c r="A47">
+        <v>3</v>
+      </c>
+      <c r="B47">
+        <v>14</v>
+      </c>
+      <c r="C47">
         <v>4</v>
       </c>
-      <c r="B47">
-        <v>1</v>
-      </c>
-      <c r="C47">
-        <v>5</v>
-      </c>
       <c r="D47" t="str">
-        <v>Tell me about yourself</v>
+        <v>unethical practice</v>
       </c>
       <c r="E47" t="str">
-        <v>hãy giới thiệu về bản thân bạn</v>
+        <v>for that reason</v>
       </c>
       <c r="F47" t="str">
-        <v>Intro</v>
+        <v>line in the sand</v>
       </c>
       <c r="G47" t="str">
-        <v>18 years of experience</v>
+        <v>rejected</v>
       </c>
       <c r="H47" t="str">
-        <v>18 năm kinh nghiệm trong ngành</v>
+        <v/>
       </c>
       <c r="I47" t="str">
-        <v>Keyword</v>
+        <v>hành vi phi đạo đức</v>
       </c>
       <c r="J47" t="str">
-        <v>demonstrates how I</v>
+        <v>chính vì thế</v>
       </c>
       <c r="K47" t="str">
-        <v>chứng minh rõ việc tôi đã...</v>
+        <v>ranh giới bất khả xâm phạm</v>
       </c>
       <c r="L47" t="str">
-        <v>Logic word</v>
+        <v>bị khước từ dứt khoát</v>
       </c>
       <c r="M47" t="str">
-        <v>mastered accounting functions</v>
+        <v/>
       </c>
       <c r="N47" t="str">
-        <v>làm chủ các nghiệp vụ kế toán chuyên sâu</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O47" t="str">
-        <v>Fancy word</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P47" t="str">
-        <v>drove organizational excellence</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q47" t="str">
-        <v>thúc đẩy tổ chức phát triển vượt bậc</v>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R47" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48">
+        <v>3</v>
+      </c>
+      <c r="B48">
+        <v>15</v>
+      </c>
+      <c r="C48">
         <v>4</v>
       </c>
-      <c r="B48">
-        <v>2</v>
-      </c>
-      <c r="C48">
-        <v>5</v>
-      </c>
       <c r="D48" t="str">
-        <v>I'm not bragging but</v>
+        <v>career opportunity</v>
       </c>
       <c r="E48" t="str">
-        <v>không phải tôi khoe khoang đâu nhưng</v>
+        <v>besides</v>
       </c>
       <c r="F48" t="str">
-        <v>Intro</v>
+        <v>golden ticket</v>
       </c>
       <c r="G48" t="str">
-        <v>man of the month</v>
+        <v>seized</v>
       </c>
       <c r="H48" t="str">
-        <v>nhân viên xuất sắc của tháng</v>
+        <v/>
       </c>
       <c r="I48" t="str">
-        <v>Keyword</v>
+        <v>cơ hội nghề nghiệp</v>
       </c>
       <c r="J48" t="str">
-        <v>was awarded because of</v>
+        <v>ngoài ra</v>
       </c>
       <c r="K48" t="str">
-        <v>đã được trao tặng nhờ...</v>
+        <v>tấm vé vàng đổi đời</v>
       </c>
       <c r="L48" t="str">
-        <v>Logic word</v>
+        <v>được nắm bắt</v>
       </c>
       <c r="M48" t="str">
-        <v>exceptional newcomer mentoring</v>
+        <v/>
       </c>
       <c r="N48" t="str">
-        <v>thành tích kèm cặp người mới xuất chúng</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="O48" t="str">
-        <v>Fancy word</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="P48" t="str">
-        <v>raised overall department output</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="Q48" t="str">
-        <v>nâng tầm năng suất cho cả phòng ban</v>
+        <v>Tính từ · Ending</v>
       </c>
       <c r="R48" t="str">
-        <v>Ending</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -3092,55 +2990,55 @@
         <v>4</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49">
         <v>5</v>
       </c>
       <c r="D49" t="str">
-        <v>Specifically speaking</v>
+        <v>First and foremost</v>
       </c>
       <c r="E49" t="str">
-        <v>nói một cách cụ thể hơn</v>
+        <v>professional ethics</v>
       </c>
       <c r="F49" t="str">
-        <v>Intro</v>
+        <v>while</v>
       </c>
       <c r="G49" t="str">
-        <v>reconciliation of transactions</v>
+        <v>moral compass</v>
       </c>
       <c r="H49" t="str">
-        <v>khâu đối chiếu các giao dịch</v>
+        <v>unbending</v>
       </c>
       <c r="I49" t="str">
-        <v>Keyword</v>
+        <v>Trước hết và quan trọng nhất</v>
       </c>
       <c r="J49" t="str">
-        <v>requires strict diligence and</v>
+        <v>đạo đức nghề nghiệp</v>
       </c>
       <c r="K49" t="str">
-        <v>đòi hỏi sự cẩn trọng cao độ và...</v>
+        <v>trong khi</v>
       </c>
       <c r="L49" t="str">
-        <v>Logic word</v>
+        <v>kim chỉ nam dẫn đường</v>
       </c>
       <c r="M49" t="str">
-        <v>flawless bookkeeping precision</v>
+        <v>không nhân nhượng</v>
       </c>
       <c r="N49" t="str">
-        <v>độ chuẩn xác tuyệt đối trong lưu giữ sổ sách</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O49" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P49" t="str">
-        <v>prevented multi-million audits</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q49" t="str">
-        <v>ngăn chặn các rủi ro kiểm toán hàng triệu đô</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R49" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
       </c>
     </row>
     <row r="50">
@@ -3148,55 +3046,55 @@
         <v>4</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C50">
         <v>5</v>
       </c>
       <c r="D50" t="str">
-        <v>Besides that point</v>
+        <v>To tell you the truth</v>
       </c>
       <c r="E50" t="str">
-        <v>bên cạnh điểm sáng đó ra</v>
+        <v>financial modeling</v>
       </c>
       <c r="F50" t="str">
-        <v>Intro</v>
+        <v>however</v>
       </c>
       <c r="G50" t="str">
-        <v>energetic senior student</v>
+        <v>hard nut</v>
       </c>
       <c r="H50" t="str">
-        <v>sinh viên năm cuối đầy nhiệt huyết</v>
+        <v>conquered</v>
       </c>
       <c r="I50" t="str">
-        <v>Keyword</v>
+        <v>Thành thật giãi bày</v>
       </c>
       <c r="J50" t="str">
-        <v>balanced coursework while</v>
+        <v>mô hình hóa tài chính</v>
       </c>
       <c r="K50" t="str">
-        <v>đã cân bằng việc học tại trường trong khi...</v>
+        <v>tuy nhiên</v>
       </c>
       <c r="L50" t="str">
-        <v>Logic word</v>
+        <v>bài toán hóc búa</v>
       </c>
       <c r="M50" t="str">
-        <v>leading e-commerce sales</v>
+        <v>được chinh phục</v>
       </c>
       <c r="N50" t="str">
-        <v>dẫn dắt các chiến dịch bán hàng trực tuyến</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O50" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P50" t="str">
-        <v>surpassed quarterly target goals</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q50" t="str">
-        <v>vượt xa các chỉ tiêu doanh số theo quý</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R50" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
       </c>
     </row>
     <row r="51">
@@ -3204,55 +3102,55 @@
         <v>4</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C51">
         <v>5</v>
       </c>
       <c r="D51" t="str">
-        <v>Soon after that</v>
+        <v>In my humble opinion</v>
       </c>
       <c r="E51" t="str">
-        <v>ngay sau cột mốc đó</v>
+        <v>cross-functional team</v>
       </c>
       <c r="F51" t="str">
-        <v>Intro</v>
+        <v>otherwise</v>
       </c>
       <c r="G51" t="str">
-        <v>company restructure plan</v>
+        <v>silo mentality</v>
       </c>
       <c r="H51" t="str">
-        <v>kế hoạch tái cơ cấu doanh nghiệp</v>
+        <v>collaborative</v>
       </c>
       <c r="I51" t="str">
-        <v>Keyword</v>
+        <v>Theo ý kiến khiêm tốn của tôi</v>
       </c>
       <c r="J51" t="str">
-        <v>opened new avenues to</v>
+        <v>nhóm liên phòng ban</v>
       </c>
       <c r="K51" t="str">
-        <v>đã mở ra cơ hội lớn để...</v>
+        <v>nếu không</v>
       </c>
       <c r="L51" t="str">
-        <v>Logic word</v>
+        <v>tư duy cục bộ</v>
       </c>
       <c r="M51" t="str">
-        <v>eliminate redundant procedures</v>
+        <v>hợp tác khăng khít</v>
       </c>
       <c r="N51" t="str">
-        <v>loại bỏ các quy trình thừa thãi rườm rà</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O51" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P51" t="str">
-        <v>streamlined overall workflow</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q51" t="str">
-        <v>tinh gọn toàn bộ guồng quay công việc</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R51" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
       </c>
     </row>
     <row r="52">
@@ -3260,55 +3158,55 @@
         <v>4</v>
       </c>
       <c r="B52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C52">
         <v>5</v>
       </c>
       <c r="D52" t="str">
-        <v>In other words</v>
+        <v>As far as I'm concerned</v>
       </c>
       <c r="E52" t="str">
-        <v>nói theo một cách khác</v>
+        <v>cost reduction</v>
       </c>
       <c r="F52" t="str">
-        <v>Intro</v>
+        <v>therefore</v>
       </c>
       <c r="G52" t="str">
-        <v>uncompromising integrity</v>
+        <v>low-hanging fruit</v>
       </c>
       <c r="H52" t="str">
-        <v>sự chính trực không bao giờ thỏa hiệp</v>
+        <v>optimized</v>
       </c>
       <c r="I52" t="str">
-        <v>Keyword</v>
+        <v>Theo góc nhìn chuyên môn của tôi</v>
       </c>
       <c r="J52" t="str">
-        <v>serves as my</v>
+        <v>cắt giảm chi phí</v>
       </c>
       <c r="K52" t="str">
-        <v>đóng vai trò là...</v>
+        <v>do đó</v>
       </c>
       <c r="L52" t="str">
-        <v>Logic word</v>
+        <v>thành quả dễ gặt hái</v>
       </c>
       <c r="M52" t="str">
-        <v>intangible internal anchor</v>
+        <v>được tối ưu</v>
       </c>
       <c r="N52" t="str">
-        <v>điểm tựa nội lực vô hình vững chắc</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O52" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P52" t="str">
-        <v>guides every ethical decision</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q52" t="str">
-        <v>dẫn lối cho mọi quyết định chuẩn mực đạo đức</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R52" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
       </c>
     </row>
     <row r="53">
@@ -3316,55 +3214,55 @@
         <v>4</v>
       </c>
       <c r="B53">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C53">
         <v>5</v>
       </c>
       <c r="D53" t="str">
-        <v>As long as</v>
+        <v>Believe it or not</v>
       </c>
       <c r="E53" t="str">
-        <v>miễn là chúng ta</v>
+        <v>cloud migration</v>
       </c>
       <c r="F53" t="str">
-        <v>Intro</v>
+        <v>eventually</v>
       </c>
       <c r="G53" t="str">
-        <v>open-ended questions</v>
+        <v>smooth sailing</v>
       </c>
       <c r="H53" t="str">
-        <v>những câu hỏi phỏng vấn mở</v>
+        <v>seamless</v>
       </c>
       <c r="I53" t="str">
-        <v>Keyword</v>
+        <v>Dù tin hay không</v>
       </c>
       <c r="J53" t="str">
-        <v>are answered with honest</v>
+        <v>chuyển đổi dữ liệu đám mây</v>
       </c>
       <c r="K53" t="str">
-        <v>được đối đáp bằng sự chân thành cùng...</v>
+        <v>sau cùng</v>
       </c>
       <c r="L53" t="str">
-        <v>Logic word</v>
+        <v>thuận buồm xuôi gió</v>
       </c>
       <c r="M53" t="str">
-        <v>proven track record</v>
+        <v>liền mạch trơn tru</v>
       </c>
       <c r="N53" t="str">
-        <v>những chiến tích thực tế đã được kiểm chứng</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O53" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P53" t="str">
-        <v>convince any hiring panel</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q53" t="str">
-        <v>chắc chắn thuyết phục được mọi nhà tuyển dụng</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R53" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
       </c>
     </row>
     <row r="54">
@@ -3372,55 +3270,55 @@
         <v>4</v>
       </c>
       <c r="B54">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C54">
         <v>5</v>
       </c>
       <c r="D54" t="str">
-        <v>Fortunately enough</v>
+        <v>From my experience</v>
       </c>
       <c r="E54" t="str">
-        <v>thật may mắn khi mà</v>
+        <v>quarterly closing</v>
       </c>
       <c r="F54" t="str">
-        <v>Intro</v>
+        <v>meanwhile</v>
       </c>
       <c r="G54" t="str">
-        <v>monthly balance sheet</v>
+        <v>cool head</v>
       </c>
       <c r="H54" t="str">
-        <v>bảng cân đối kế toán hàng tháng</v>
+        <v>focused</v>
       </c>
       <c r="I54" t="str">
-        <v>Keyword</v>
+        <v>Từ kinh nghiệm thực tế của tôi</v>
       </c>
       <c r="J54" t="str">
-        <v>was verified thoroughly through</v>
+        <v>chốt sổ kế toán quý</v>
       </c>
       <c r="K54" t="str">
-        <v>đã được thẩm định kỹ lưỡng nhờ...</v>
+        <v>đồng thời</v>
       </c>
       <c r="L54" t="str">
-        <v>Logic word</v>
+        <v>cái đầu lạnh điềm tĩnh</v>
       </c>
       <c r="M54" t="str">
-        <v>rigorous internal review</v>
+        <v>tập trung cao độ</v>
       </c>
       <c r="N54" t="str">
-        <v>quy trình rà soát nội bộ gắt gao</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O54" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P54" t="str">
-        <v>passed external audit smoothly</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q54" t="str">
-        <v>vượt qua kỳ kiểm toán bên ngoài trơn tru</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R54" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
       </c>
     </row>
     <row r="55">
@@ -3428,55 +3326,55 @@
         <v>4</v>
       </c>
       <c r="B55">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C55">
         <v>5</v>
       </c>
       <c r="D55" t="str">
-        <v>For better or worse</v>
+        <v>Honestly speaking</v>
       </c>
       <c r="E55" t="str">
-        <v>dù tình thế có ra sao</v>
+        <v>junior analyst</v>
       </c>
       <c r="F55" t="str">
-        <v>Intro</v>
+        <v>if</v>
       </c>
       <c r="G55" t="str">
-        <v>unpredictable market shifts</v>
+        <v>eager beaver</v>
       </c>
       <c r="H55" t="str">
-        <v>những biến động thị trường khôn lường</v>
+        <v>promising</v>
       </c>
       <c r="I55" t="str">
-        <v>Keyword</v>
+        <v>Nói một cách chân thành</v>
       </c>
       <c r="J55" t="str">
-        <v>demanded that we adopt</v>
+        <v>chuyên viên phân tích trẻ</v>
       </c>
       <c r="K55" t="str">
-        <v>đòi hỏi chúng tôi phải áp dụng...</v>
+        <v>nếu</v>
       </c>
       <c r="L55" t="str">
-        <v>Logic word</v>
+        <v>người chăm chỉ nhiệt thành</v>
       </c>
       <c r="M55" t="str">
-        <v>innovative digital strategies</v>
+        <v>đầy triển vọng</v>
       </c>
       <c r="N55" t="str">
-        <v>những chiến lược chuyển đổi số đột phá</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O55" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P55" t="str">
-        <v>strengthened long-term resilience</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q55" t="str">
-        <v>gia tăng sức bền bỉ dài hạn cho công ty</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R55" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
       </c>
     </row>
     <row r="56">
@@ -3484,55 +3382,55 @@
         <v>4</v>
       </c>
       <c r="B56">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C56">
         <v>5</v>
       </c>
       <c r="D56" t="str">
-        <v>To be specific</v>
+        <v>Don't get me wrong</v>
       </c>
       <c r="E56" t="str">
-        <v>nói cụ thể hơn nữa nhé</v>
+        <v>internal audit</v>
       </c>
       <c r="F56" t="str">
-        <v>Intro</v>
+        <v>nevertheless</v>
       </c>
       <c r="G56" t="str">
-        <v>clearance sales promotion</v>
+        <v>fine-tooth comb</v>
       </c>
       <c r="H56" t="str">
-        <v>đợt khuyến mãi xả hàng quy mô lớn</v>
+        <v>rigorous</v>
       </c>
       <c r="I56" t="str">
-        <v>Keyword</v>
+        <v>Đừng hiểu sai ý tôi</v>
       </c>
       <c r="J56" t="str">
-        <v>succeeded mainly because of</v>
+        <v>kiểm toán nội bộ</v>
       </c>
       <c r="K56" t="str">
-        <v>thành công vang dội chủ yếu nhờ...</v>
+        <v>dù vậy</v>
       </c>
       <c r="L56" t="str">
-        <v>Logic word</v>
+        <v>soi kỹ từng chân tơ kẽ tóc</v>
       </c>
       <c r="M56" t="str">
-        <v>persuasive marketing copy</v>
+        <v>ngặt nghèo chuẩn chỉ</v>
       </c>
       <c r="N56" t="str">
-        <v>nội dung quảng bá đánh trúng tâm lý người mua</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O56" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P56" t="str">
-        <v>cleared aging warehouse inventory</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q56" t="str">
-        <v>dọn sạch hàng lưu kho lâu ngày trong kho</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R56" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
       </c>
     </row>
     <row r="57">
@@ -3540,55 +3438,55 @@
         <v>4</v>
       </c>
       <c r="B57">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C57">
         <v>5</v>
       </c>
       <c r="D57" t="str">
-        <v>Take your time</v>
+        <v>As a matter of fact</v>
       </c>
       <c r="E57" t="str">
-        <v>cứ thong thả xem xét</v>
+        <v>budget variance</v>
       </c>
       <c r="F57" t="str">
-        <v>Intro</v>
+        <v>before that</v>
       </c>
       <c r="G57" t="str">
-        <v>academic credentials portfolio</v>
+        <v>smoking gun</v>
       </c>
       <c r="H57" t="str">
-        <v>bộ hồ sơ thành tích học tập</v>
+        <v>detected</v>
       </c>
       <c r="I57" t="str">
-        <v>Keyword</v>
+        <v>Trên thực tế kiểm chứng</v>
       </c>
       <c r="J57" t="str">
-        <v>proves how thoroughly I</v>
+        <v>chênh lệch ngân sách</v>
       </c>
       <c r="K57" t="str">
-        <v>chứng minh việc tôi đã...</v>
+        <v>trước đó</v>
       </c>
       <c r="L57" t="str">
-        <v>Logic word</v>
+        <v>bằng chứng rõ mười mươi</v>
       </c>
       <c r="M57" t="str">
-        <v>mastered economic principles</v>
+        <v>được phát hiện</v>
       </c>
       <c r="N57" t="str">
-        <v>lĩnh hội sâu sắc các nguyên lý kinh tế học</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O57" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P57" t="str">
-        <v>ready for senior responsibilities</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q57" t="str">
-        <v>hoàn toàn sẵn sàng cho các trọng trách lớn</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R57" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
       </c>
     </row>
     <row r="58">
@@ -3596,55 +3494,55 @@
         <v>4</v>
       </c>
       <c r="B58">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C58">
         <v>5</v>
       </c>
       <c r="D58" t="str">
-        <v>People often say</v>
+        <v>Just to clarify</v>
       </c>
       <c r="E58" t="str">
-        <v>người ta thường hay nói rằng</v>
+        <v>emergency reserve</v>
       </c>
       <c r="F58" t="str">
-        <v>Intro</v>
+        <v>in addition</v>
       </c>
       <c r="G58" t="str">
-        <v>harmonious office collaboration</v>
+        <v>financial cushion</v>
       </c>
       <c r="H58" t="str">
-        <v>sự đồng lòng gắn kết trong văn phòng</v>
+        <v>safe</v>
       </c>
       <c r="I58" t="str">
-        <v>Keyword</v>
+        <v>Chỉ để làm rõ hơn</v>
       </c>
       <c r="J58" t="str">
-        <v>flourishes only when we</v>
+        <v>khoản dự phòng khẩn cấp</v>
       </c>
       <c r="K58" t="str">
-        <v>chỉ đơm hoa kết trái một khi chúng ta...</v>
+        <v>hơn nữa</v>
       </c>
       <c r="L58" t="str">
-        <v>Logic word</v>
+        <v>tấm đệm tài chính</v>
       </c>
       <c r="M58" t="str">
-        <v>cultivate mutual respect</v>
+        <v>an toàn tuyệt đối</v>
       </c>
       <c r="N58" t="str">
-        <v>biết tôn trọng và lắng nghe lẫn nhau</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O58" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P58" t="str">
-        <v>elevates overall team morale</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q58" t="str">
-        <v>vực dậy tinh thần cho toàn thể đồng đội</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R58" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
       </c>
     </row>
     <row r="59">
@@ -3652,55 +3550,55 @@
         <v>4</v>
       </c>
       <c r="B59">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C59">
         <v>5</v>
       </c>
       <c r="D59" t="str">
-        <v>No worries at all</v>
+        <v>By all accounts</v>
       </c>
       <c r="E59" t="str">
-        <v>hoàn toàn không có gì phải lo</v>
+        <v>project leader</v>
       </c>
       <c r="F59" t="str">
-        <v>Intro</v>
+        <v>next</v>
       </c>
       <c r="G59" t="str">
-        <v>temporary budget constraint</v>
+        <v>driving force</v>
       </c>
       <c r="H59" t="str">
-        <v>những hạn chế ngân sách tạm thời</v>
+        <v>inspirational</v>
       </c>
       <c r="I59" t="str">
-        <v>Keyword</v>
+        <v>Theo đánh giá chung</v>
       </c>
       <c r="J59" t="str">
-        <v>can be managed by</v>
+        <v>người dẫn dắt dự án</v>
       </c>
       <c r="K59" t="str">
-        <v>đều có thể được tháo gỡ nhờ...</v>
+        <v>tiếp theo</v>
       </c>
       <c r="L59" t="str">
-        <v>Logic word</v>
+        <v>đầu tàu kéo tiến độ</v>
       </c>
       <c r="M59" t="str">
-        <v>optimizing core resources</v>
+        <v>truyền cảm hứng</v>
       </c>
       <c r="N59" t="str">
-        <v>việc tối ưu hóa các nguồn lực cốt lõi</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O59" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P59" t="str">
-        <v>delivers all project targets</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q59" t="str">
-        <v>vẫn hoàn thành mọi mục tiêu dự án đề ra</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R59" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
       </c>
     </row>
     <row r="60">
@@ -3708,55 +3606,55 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C60">
         <v>5</v>
       </c>
       <c r="D60" t="str">
-        <v>What do you say</v>
+        <v>To put it another way</v>
       </c>
       <c r="E60" t="str">
-        <v>bạn nghĩ thế nào nếu</v>
+        <v>client trust</v>
       </c>
       <c r="F60" t="str">
-        <v>Intro</v>
+        <v>in other words</v>
       </c>
       <c r="G60" t="str">
-        <v>restructuring accounting team</v>
+        <v>bread and butter</v>
       </c>
       <c r="H60" t="str">
-        <v>việc tái tổ chức lại bộ phận kế toán</v>
+        <v>vital</v>
       </c>
       <c r="I60" t="str">
-        <v>Keyword</v>
+        <v>Nói bằng cách khác</v>
       </c>
       <c r="J60" t="str">
-        <v>empowers our staff with</v>
+        <v>niềm tin của khách hàng</v>
       </c>
       <c r="K60" t="str">
-        <v>sẽ trao quyền cho đội ngũ với...</v>
+        <v>nói cách khác</v>
       </c>
       <c r="L60" t="str">
-        <v>Logic word</v>
+        <v>miếng cơm manh áo cốt lõi</v>
       </c>
       <c r="M60" t="str">
-        <v>cutting-edge automation tools</v>
+        <v>sống còn</v>
       </c>
       <c r="N60" t="str">
-        <v>những công cụ tự động hóa hàng đầu</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O60" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P60" t="str">
-        <v>doubles monthly operational efficiency</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q60" t="str">
-        <v>nhân đôi hiệu quả vận hành hằng tháng</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R60" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
       </c>
     </row>
     <row r="61">
@@ -3764,60 +3662,172 @@
         <v>4</v>
       </c>
       <c r="B61">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C61">
         <v>5</v>
       </c>
       <c r="D61" t="str">
-        <v>Shall we conclude</v>
+        <v>Keep in mind</v>
       </c>
       <c r="E61" t="str">
-        <v>chúng ta cùng khép lại bằng việc</v>
+        <v>compliance regulation</v>
       </c>
       <c r="F61" t="str">
-        <v>Intro</v>
+        <v>as long as</v>
       </c>
       <c r="G61" t="str">
-        <v>consistent work experience</v>
+        <v>ahead of curve</v>
       </c>
       <c r="H61" t="str">
-        <v>bề dày kinh nghiệm công tác vững vàng</v>
+        <v>bulletproof</v>
       </c>
       <c r="I61" t="str">
-        <v>Keyword</v>
+        <v>Hãy luôn ghi nhớ</v>
       </c>
       <c r="J61" t="str">
-        <v>combined harmoniously with</v>
+        <v>quy định tuân thủ pháp lý</v>
       </c>
       <c r="K61" t="str">
-        <v>kết hợp hài hòa cùng với...</v>
+        <v>miễn là</v>
       </c>
       <c r="L61" t="str">
-        <v>Logic word</v>
+        <v>đi trước đón đầu</v>
       </c>
       <c r="M61" t="str">
-        <v>unrelenting proactive energy</v>
+        <v>vững vàng không sơ hở</v>
       </c>
       <c r="N61" t="str">
-        <v>nguồn năng lượng chủ động không ngừng nghỉ</v>
+        <v>Cụm mào đầu · Intro</v>
       </c>
       <c r="O61" t="str">
-        <v>Fancy word</v>
+        <v>Danh từ · Keyword</v>
       </c>
       <c r="P61" t="str">
-        <v>makes me ideal candidate</v>
+        <v>Từ nối · Logic word</v>
       </c>
       <c r="Q61" t="str">
-        <v>giúp tôi trở thành ứng viên sáng giá nhất</v>
+        <v>Ẩn dụ · Fancy word</v>
       </c>
       <c r="R61" t="str">
-        <v>Ending</v>
+        <v>Tính từ · Ending</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>4</v>
+      </c>
+      <c r="B62">
+        <v>14</v>
+      </c>
+      <c r="C62">
+        <v>5</v>
+      </c>
+      <c r="D62" t="str">
+        <v>You can be sure that</v>
+      </c>
+      <c r="E62" t="str">
+        <v>final report</v>
+      </c>
+      <c r="F62" t="str">
+        <v>then</v>
+      </c>
+      <c r="G62" t="str">
+        <v>clean sheet</v>
+      </c>
+      <c r="H62" t="str">
+        <v>flawless</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Bạn có thể chắc chắn rằng</v>
+      </c>
+      <c r="J62" t="str">
+        <v>báo cáo quyết toán cuối cùng</v>
+      </c>
+      <c r="K62" t="str">
+        <v>sau đó</v>
+      </c>
+      <c r="L62" t="str">
+        <v>hồ sơ sạch tinh tươm</v>
+      </c>
+      <c r="M62" t="str">
+        <v>hoàn hảo</v>
+      </c>
+      <c r="N62" t="str">
+        <v>Cụm mào đầu · Intro</v>
+      </c>
+      <c r="O62" t="str">
+        <v>Danh từ · Keyword</v>
+      </c>
+      <c r="P62" t="str">
+        <v>Từ nối · Logic word</v>
+      </c>
+      <c r="Q62" t="str">
+        <v>Cụm gợi hình · Fancy word</v>
+      </c>
+      <c r="R62" t="str">
+        <v>Tính từ · Ending</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>4</v>
+      </c>
+      <c r="B63">
+        <v>15</v>
+      </c>
+      <c r="C63">
+        <v>5</v>
+      </c>
+      <c r="D63" t="str">
+        <v>All in all</v>
+      </c>
+      <c r="E63" t="str">
+        <v>finance career</v>
+      </c>
+      <c r="F63" t="str">
+        <v>finally</v>
+      </c>
+      <c r="G63" t="str">
+        <v>true calling</v>
+      </c>
+      <c r="H63" t="str">
+        <v>fulfilling</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Tóm lại mọi điều</v>
+      </c>
+      <c r="J63" t="str">
+        <v>con đường sự nghiệp tài chính</v>
+      </c>
+      <c r="K63" t="str">
+        <v>cuối cùng</v>
+      </c>
+      <c r="L63" t="str">
+        <v>tiếng gọi đam mê đích thực</v>
+      </c>
+      <c r="M63" t="str">
+        <v>viên mãn trọn vẹn</v>
+      </c>
+      <c r="N63" t="str">
+        <v>Cụm mào đầu · Intro</v>
+      </c>
+      <c r="O63" t="str">
+        <v>Danh từ · Keyword</v>
+      </c>
+      <c r="P63" t="str">
+        <v>Từ nối · Logic word</v>
+      </c>
+      <c r="Q63" t="str">
+        <v>Ẩn dụ · Fancy word</v>
+      </c>
+      <c r="R63" t="str">
+        <v>Tính từ · Ending</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R63"/>
   </ignoredErrors>
 </worksheet>
 </file>